--- a/data/trans_bre/P15A-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 0,52</t>
+          <t>-2,7; 0,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 3,56</t>
+          <t>-0,13; 3,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,24</t>
+          <t>-1,26; 2,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,73</t>
+          <t>-2,07; 1,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-62,74; 26,53</t>
+          <t>-65,42; 29,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 257,81</t>
+          <t>-9,72; 264,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-41,43; 134,89</t>
+          <t>-42,42; 152,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 111,57</t>
+          <t>-47,27; 104,01</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 0,5</t>
+          <t>-3,19; 0,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,37</t>
+          <t>-1,87; 1,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,53</t>
+          <t>-2,48; 0,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,43</t>
+          <t>-1,12; 2,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-57,54; 19,58</t>
+          <t>-55,93; 13,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 66,08</t>
+          <t>-47,76; 64,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,77; 24,04</t>
+          <t>-60,67; 30,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 175,28</t>
+          <t>-34,57; 205,9</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,8</t>
+          <t>-2,0; 1,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,86</t>
+          <t>-1,54; 1,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,87</t>
+          <t>-1,44; 0,97</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,86</t>
+          <t>-1,19; 1,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-45,62; 70,26</t>
+          <t>-44,32; 71,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-47,15; 102,97</t>
+          <t>-46,61; 109,59</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-67,61; 96,71</t>
+          <t>-67,02; 99,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,47; 172,1</t>
+          <t>-43,82; 163,1</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 0,16</t>
+          <t>-3,05; 0,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,19</t>
+          <t>-2,97; 0,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,97</t>
+          <t>-1,31; 2,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,34</t>
+          <t>-0,88; 1,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 9,65</t>
+          <t>-65,54; 12,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,97; 15,42</t>
+          <t>-64,29; 5,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,23; 91,43</t>
+          <t>-35,75; 99,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,66; 109,01</t>
+          <t>-34,84; 117,72</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; -0,16</t>
+          <t>-1,89; 0,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,74</t>
+          <t>-0,9; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,68</t>
+          <t>-0,97; 0,58</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,24</t>
+          <t>-0,42; 1,18</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,11; -4,51</t>
+          <t>-44,44; -0,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 30,62</t>
+          <t>-27,6; 27,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-30,78; 29,27</t>
+          <t>-33,54; 25,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 72,31</t>
+          <t>-15,6; 69,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15A-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 0,67</t>
+          <t>-2,81; 0,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,47</t>
+          <t>-0,29; 3,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,29</t>
+          <t>-1,31; 2,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 1,66</t>
+          <t>-2,36; 1,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,42; 29,1</t>
+          <t>-66,59; 35,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 264,4</t>
+          <t>-16,64; 239,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 152,27</t>
+          <t>-40,84; 135,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-47,27; 104,01</t>
+          <t>-51,86; 85,91</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>-0,1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>-3,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,44</t>
+          <t>-3,28; 0,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 1,29</t>
+          <t>-1,76; 1,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 0,66</t>
+          <t>-2,45; 0,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,48</t>
+          <t>-1,83; 1,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,93; 13,07</t>
+          <t>-57,91; 11,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,76; 64,27</t>
+          <t>-46,73; 65,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,67; 30,16</t>
+          <t>-62,41; 27,7</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,57; 205,9</t>
+          <t>-45,93; 74,07</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,87</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>46,27%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,9</t>
+          <t>-1,96; 2,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 1,88</t>
+          <t>-1,53; 1,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,97</t>
+          <t>-1,44; 1,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,86</t>
+          <t>-0,48; 2,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-44,32; 71,04</t>
+          <t>-43,91; 91,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 109,59</t>
+          <t>-45,96; 105,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-67,02; 99,09</t>
+          <t>-67,31; 124,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 163,1</t>
+          <t>-23,64; 198,21</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,32</t>
+          <t>0,58</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,22</t>
+          <t>-2,86; 0,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,09</t>
+          <t>-2,93; 0,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,15</t>
+          <t>-1,12; 2,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,41</t>
+          <t>-0,54; 1,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,54; 12,34</t>
+          <t>-65,11; 12,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-64,29; 5,34</t>
+          <t>-63,54; 11,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 99,61</t>
+          <t>-30,37; 96,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,84; 117,72</t>
+          <t>-24,42; 156,1</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>14,21%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,01</t>
+          <t>-1,83; -0,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 0,7</t>
+          <t>-0,96; 0,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 0,58</t>
+          <t>-0,9; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 1,18</t>
+          <t>-0,41; 1,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-44,44; -0,01</t>
+          <t>-43,63; -4,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 27,58</t>
+          <t>-28,15; 26,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 25,8</t>
+          <t>-30,35; 30,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 69,62</t>
+          <t>-14,28; 62,47</t>
         </is>
       </c>
     </row>
